--- a/A21 - rentgen - kopie/A21.xlsx
+++ b/A21 - rentgen - kopie/A21.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jonas\Documents\Praktikum-IV\A21 - rentgen\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jonas\Documents\Praktikum-IV\A21 - rentgen - kopie\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB76D16A-D3BD-41B9-9F33-8A8451C0FD3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCF08714-37AB-489B-918E-9A08D2C7FFD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B8DF00CB-DCF1-4C1A-ABA1-0DE29D1463BD}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="38">
   <si>
     <t>Fitování lineárních grafů 1. úkolu</t>
   </si>
@@ -96,12 +96,69 @@
   </si>
   <si>
     <t>Mo 33 kV</t>
+  </si>
+  <si>
+    <t>K_beta, n=1</t>
+  </si>
+  <si>
+    <t>K_alpha, n=1</t>
+  </si>
+  <si>
+    <t>K_alpha, n=2</t>
+  </si>
+  <si>
+    <t>K_beta, n=2</t>
+  </si>
+  <si>
+    <t>Zr</t>
+  </si>
+  <si>
+    <t>Ni</t>
+  </si>
+  <si>
+    <t>lambda_teor / pm</t>
+  </si>
+  <si>
+    <t>1/sqrt(lambda)</t>
+  </si>
+  <si>
+    <t>a / 10^{-3} pm^{-1/2}</t>
+  </si>
+  <si>
+    <t>b / 10^{-3} pm^{-1/2}</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>R_\omega / 10^{16} s^{-1}</t>
+  </si>
+  <si>
+    <t>\theta_1 / °</t>
+  </si>
+  <si>
+    <t>\theta_2 / °</t>
+  </si>
+  <si>
+    <t>\lambda_1</t>
+  </si>
+  <si>
+    <t>\lambda_2</t>
+  </si>
+  <si>
+    <t>řád</t>
+  </si>
+  <si>
+    <t>dtheta/dlambda / mm^(-1)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="167" formatCode="0.0"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -132,8 +189,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normální" xfId="0" builtinId="0"/>
@@ -468,13 +528,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59B71BA6-80FA-438B-B425-C6D36BB24D85}">
-  <dimension ref="B3:H27"/>
+  <dimension ref="A3:H42"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="3" width="16.109375" customWidth="1"/>
-    <col min="4" max="4" width="14.77734375" customWidth="1"/>
+    <col min="2" max="2" width="19" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="25" customWidth="1"/>
     <col min="5" max="5" width="18.5546875" customWidth="1"/>
     <col min="6" max="6" width="10.88671875" customWidth="1"/>
+    <col min="7" max="7" width="15.6640625" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -519,8 +581,8 @@
         <v>3.7500000000000001E-4</v>
       </c>
       <c r="H5">
-        <f>(1.602*10^(-19)*2*G5)/(299792458)</f>
-        <v>4.0077726038057973E-31</v>
+        <f>(1.602*10^(-19)*2*G5*201.4*10^(-5))/(299792458)</f>
+        <v>8.071654024064876E-34</v>
       </c>
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.3">
@@ -584,6 +646,12 @@
       <c r="F11" t="s">
         <v>8</v>
       </c>
+      <c r="G11" t="s">
+        <v>26</v>
+      </c>
+      <c r="H11" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
@@ -599,17 +667,39 @@
       <c r="E12" t="s">
         <v>12</v>
       </c>
+      <c r="F12" s="2">
+        <f>2*201.4*SIN(D12*0.0174532925)</f>
+        <v>137.10488267550221</v>
+      </c>
+      <c r="G12">
+        <v>140.4</v>
+      </c>
+      <c r="H12">
+        <f>1/SQRT(F12)</f>
+        <v>8.5403081136830428E-2</v>
+      </c>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C13">
         <v>44.4</v>
       </c>
       <c r="D13">
-        <f t="shared" ref="D13:D36" si="1">C13/2</f>
+        <f t="shared" ref="D13:D31" si="1">C13/2</f>
         <v>22.2</v>
       </c>
       <c r="E13" t="s">
         <v>13</v>
+      </c>
+      <c r="F13" s="2">
+        <f t="shared" ref="F13:F31" si="2">2*201.4*SIN(D13*0.0174532925)</f>
+        <v>152.19426876536235</v>
+      </c>
+      <c r="G13">
+        <v>154.1</v>
+      </c>
+      <c r="H13">
+        <f t="shared" ref="H13:H31" si="3">1/SQRT(F13)</f>
+        <v>8.1058927047863744E-2</v>
       </c>
     </row>
     <row r="14" spans="2:8" x14ac:dyDescent="0.3">
@@ -623,6 +713,17 @@
         <f t="shared" si="1"/>
         <v>19.899999999999999</v>
       </c>
+      <c r="E14" t="s">
+        <v>20</v>
+      </c>
+      <c r="F14" s="2">
+        <f t="shared" si="2"/>
+        <v>137.10488267550221</v>
+      </c>
+      <c r="H14">
+        <f t="shared" si="3"/>
+        <v>8.5403081136830428E-2</v>
+      </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C15">
@@ -632,31 +733,67 @@
         <f t="shared" si="1"/>
         <v>22.1</v>
       </c>
+      <c r="E15" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="2">
+        <f t="shared" si="2"/>
+        <v>151.54313302804721</v>
+      </c>
+      <c r="H15">
+        <f t="shared" si="3"/>
+        <v>8.1232883430024966E-2</v>
+      </c>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B16" t="s">
+      <c r="C16">
+        <v>86.6</v>
+      </c>
+      <c r="D16">
+        <f t="shared" si="1"/>
+        <v>43.3</v>
+      </c>
+      <c r="E16" t="s">
+        <v>23</v>
+      </c>
+      <c r="F16" s="2">
+        <f>2*201.4*SIN(D16*0.0174532925)/2</f>
+        <v>138.12381615300086</v>
+      </c>
+      <c r="G16">
+        <v>139.6</v>
+      </c>
+      <c r="H16">
+        <f t="shared" si="3"/>
+        <v>8.5087490598633714E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C17">
+        <v>99.1</v>
+      </c>
+      <c r="D17">
+        <f t="shared" si="1"/>
+        <v>49.55</v>
+      </c>
+      <c r="E17" t="s">
+        <v>22</v>
+      </c>
+      <c r="F17" s="2">
+        <f>2*201.4*SIN(D17*0.0174532925)/2</f>
+        <v>153.25984653277058</v>
+      </c>
+      <c r="G17">
+        <v>154.9</v>
+      </c>
+      <c r="H17">
+        <f t="shared" si="3"/>
+        <v>8.0776644206137435E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B18" t="s">
         <v>15</v>
-      </c>
-      <c r="C16">
-        <v>39.799999999999997</v>
-      </c>
-      <c r="D16">
-        <f t="shared" si="1"/>
-        <v>19.899999999999999</v>
-      </c>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C17">
-        <v>44.4</v>
-      </c>
-      <c r="D17">
-        <f t="shared" si="1"/>
-        <v>22.2</v>
-      </c>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B18" t="s">
-        <v>16</v>
       </c>
       <c r="C18">
         <v>39.799999999999997</v>
@@ -665,8 +802,19 @@
         <f t="shared" si="1"/>
         <v>19.899999999999999</v>
       </c>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="E18" t="s">
+        <v>20</v>
+      </c>
+      <c r="F18" s="2">
+        <f t="shared" si="2"/>
+        <v>137.10488267550221</v>
+      </c>
+      <c r="H18">
+        <f t="shared" si="3"/>
+        <v>8.5403081136830428E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C19">
         <v>44.4</v>
       </c>
@@ -674,41 +822,88 @@
         <f t="shared" si="1"/>
         <v>22.2</v>
       </c>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="E19" t="s">
+        <v>21</v>
+      </c>
+      <c r="F19" s="2">
+        <f t="shared" si="2"/>
+        <v>152.19426876536235</v>
+      </c>
+      <c r="H19">
+        <f t="shared" si="3"/>
+        <v>8.1058927047863744E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20">
+        <v>39.799999999999997</v>
+      </c>
+      <c r="D20">
+        <f t="shared" si="1"/>
+        <v>19.899999999999999</v>
+      </c>
+      <c r="E20" t="s">
+        <v>20</v>
+      </c>
+      <c r="F20" s="2">
+        <f t="shared" si="2"/>
+        <v>137.10488267550221</v>
+      </c>
+      <c r="H20">
+        <f t="shared" si="3"/>
+        <v>8.5403081136830428E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C21">
+        <v>44.4</v>
+      </c>
+      <c r="D21">
+        <f t="shared" si="1"/>
+        <v>22.2</v>
+      </c>
+      <c r="E21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F21" s="2">
+        <f t="shared" si="2"/>
+        <v>152.19426876536235</v>
+      </c>
+      <c r="H21">
+        <f t="shared" si="3"/>
+        <v>8.1058927047863744E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B22" t="s">
         <v>17</v>
       </c>
-      <c r="C20">
+      <c r="C22">
         <v>51.6</v>
       </c>
-      <c r="D20">
+      <c r="D22">
         <f t="shared" si="1"/>
         <v>25.8</v>
       </c>
-    </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C21">
-        <v>57.2</v>
-      </c>
-      <c r="D21">
-        <f t="shared" si="1"/>
-        <v>28.6</v>
-      </c>
-    </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B22" t="s">
-        <v>18</v>
-      </c>
-      <c r="C22">
-        <v>51.4</v>
-      </c>
-      <c r="D22">
-        <f t="shared" si="1"/>
-        <v>25.7</v>
-      </c>
-    </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="E22" t="s">
+        <v>20</v>
+      </c>
+      <c r="F22" s="2">
+        <f t="shared" si="2"/>
+        <v>175.31108664057749</v>
+      </c>
+      <c r="G22">
+        <v>175.3</v>
+      </c>
+      <c r="H22">
+        <f t="shared" si="3"/>
+        <v>7.5525795647888166E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C23">
         <v>57.2</v>
       </c>
@@ -716,44 +911,305 @@
         <f t="shared" si="1"/>
         <v>28.6</v>
       </c>
-    </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="E23" t="s">
+        <v>21</v>
+      </c>
+      <c r="F23" s="2">
+        <f t="shared" si="2"/>
+        <v>192.81708017676124</v>
+      </c>
+      <c r="G23">
+        <v>194.7</v>
+      </c>
+      <c r="H23">
+        <f t="shared" si="3"/>
+        <v>7.2015710369590563E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24">
+        <v>51.4</v>
+      </c>
+      <c r="D24">
+        <f t="shared" si="1"/>
+        <v>25.7</v>
+      </c>
+      <c r="E24" t="s">
+        <v>20</v>
+      </c>
+      <c r="F24" s="2">
+        <f t="shared" si="2"/>
+        <v>174.6778790858335</v>
+      </c>
+      <c r="H24">
+        <f t="shared" si="3"/>
+        <v>7.566256237227606E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C25">
+        <v>57.2</v>
+      </c>
+      <c r="D25">
+        <f t="shared" si="1"/>
+        <v>28.6</v>
+      </c>
+      <c r="E25" t="s">
+        <v>21</v>
+      </c>
+      <c r="F25" s="2">
+        <f t="shared" si="2"/>
+        <v>192.81708017676124</v>
+      </c>
+      <c r="H25">
+        <f t="shared" si="3"/>
+        <v>7.2015710369590563E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B26" t="s">
         <v>19</v>
       </c>
-      <c r="C24">
+      <c r="C26">
         <v>17.399999999999999</v>
       </c>
-      <c r="D24">
+      <c r="D26">
         <f t="shared" si="1"/>
         <v>8.6999999999999993</v>
       </c>
-    </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C25">
+      <c r="E26" t="s">
+        <v>20</v>
+      </c>
+      <c r="F26" s="2">
+        <f t="shared" si="2"/>
+        <v>60.927858326495546</v>
+      </c>
+      <c r="G26">
+        <v>64.400000000000006</v>
+      </c>
+      <c r="H26">
+        <f t="shared" si="3"/>
+        <v>0.12811265858695886</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C27">
         <v>19.600000000000001</v>
       </c>
-      <c r="D25">
+      <c r="D27">
         <f t="shared" si="1"/>
         <v>9.8000000000000007</v>
       </c>
-    </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C26">
+      <c r="E27" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="2">
+        <f t="shared" si="2"/>
+        <v>68.560386186501702</v>
+      </c>
+      <c r="G27">
+        <v>70.400000000000006</v>
+      </c>
+      <c r="H27">
+        <f t="shared" si="3"/>
+        <v>0.12077119745804396</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C28">
         <v>35.5</v>
       </c>
-      <c r="D26">
+      <c r="D28">
         <f t="shared" si="1"/>
         <v>17.75</v>
       </c>
-    </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C27">
+      <c r="E28" t="s">
+        <v>23</v>
+      </c>
+      <c r="F28" s="2">
+        <f>2*201.4*SIN(D28*0.0174532925)/2</f>
+        <v>61.399669756340984</v>
+      </c>
+      <c r="G28">
+        <v>63.9</v>
+      </c>
+      <c r="H28">
+        <f t="shared" si="3"/>
+        <v>0.12761948342760282</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C29">
         <v>40.5</v>
       </c>
-      <c r="D27">
+      <c r="D29">
         <f t="shared" si="1"/>
         <v>20.25</v>
+      </c>
+      <c r="E29" t="s">
+        <v>22</v>
+      </c>
+      <c r="F29" s="2">
+        <f>2*201.4*SIN(D29*0.0174532925)/2</f>
+        <v>69.7079752190986</v>
+      </c>
+      <c r="G29">
+        <v>71.2</v>
+      </c>
+      <c r="H29">
+        <f t="shared" si="3"/>
+        <v>0.11977295540570206</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B30" t="s">
+        <v>24</v>
+      </c>
+      <c r="C30">
+        <v>19.399999999999999</v>
+      </c>
+      <c r="D30">
+        <f t="shared" si="1"/>
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="F30" s="2">
+        <f t="shared" si="2"/>
+        <v>67.867522011975396</v>
+      </c>
+      <c r="H30">
+        <f t="shared" si="3"/>
+        <v>0.12138611272327374</v>
+      </c>
+    </row>
+    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B31" t="s">
+        <v>25</v>
+      </c>
+      <c r="C31">
+        <v>39.799999999999997</v>
+      </c>
+      <c r="D31">
+        <f t="shared" si="1"/>
+        <v>19.899999999999999</v>
+      </c>
+      <c r="F31" s="2">
+        <f t="shared" si="2"/>
+        <v>137.10488267550221</v>
+      </c>
+      <c r="H31">
+        <f t="shared" si="3"/>
+        <v>8.5403081136830428E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B35" t="s">
+        <v>28</v>
+      </c>
+      <c r="C35" t="s">
+        <v>29</v>
+      </c>
+      <c r="D35" t="s">
+        <v>31</v>
+      </c>
+      <c r="E35" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B36">
+        <v>3</v>
+      </c>
+      <c r="C36">
+        <v>-6.22</v>
+      </c>
+      <c r="D36" s="3">
+        <f>B36^2*8*PI()*299792458/3/10^(16)</f>
+        <v>2.2603818807706237E-6</v>
+      </c>
+      <c r="E36" s="1">
+        <f>-C36/B36</f>
+        <v>2.0733333333333333</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B37">
+        <v>3.27</v>
+      </c>
+      <c r="C37">
+        <v>-9.7899999999999991</v>
+      </c>
+      <c r="D37" s="3">
+        <f>B37^2*8*PI()*299792458/3/10^(16)</f>
+        <v>2.6855597125435789E-6</v>
+      </c>
+      <c r="E37" s="1">
+        <f>-C37/B37</f>
+        <v>2.9938837920489294</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>36</v>
+      </c>
+      <c r="B40" t="s">
+        <v>32</v>
+      </c>
+      <c r="C40" t="s">
+        <v>33</v>
+      </c>
+      <c r="D40" t="s">
+        <v>34</v>
+      </c>
+      <c r="E40" t="s">
+        <v>35</v>
+      </c>
+      <c r="F40" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41">
+        <v>1</v>
+      </c>
+      <c r="B41">
+        <v>10.3</v>
+      </c>
+      <c r="C41">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="D41">
+        <v>70.400000000000006</v>
+      </c>
+      <c r="E41">
+        <v>64.400000000000006</v>
+      </c>
+      <c r="F41" s="1">
+        <f>A41/(2*201.4*10^(-3)*COS(((B41+C41)/2)*0.0174532925))</f>
+        <v>2.5190060226006143</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <v>2</v>
+      </c>
+      <c r="B42">
+        <v>25.25</v>
+      </c>
+      <c r="C42">
+        <v>22.75</v>
+      </c>
+      <c r="D42">
+        <v>71.2</v>
+      </c>
+      <c r="E42">
+        <v>63.9</v>
+      </c>
+      <c r="F42" s="1">
+        <f>A42/(2*201.4*10^(-3)*COS(((B42+C42)/2)*0.0174532925))</f>
+        <v>5.4351354432610499</v>
       </c>
     </row>
   </sheetData>

--- a/A21 - rentgen - kopie/A21.xlsx
+++ b/A21 - rentgen - kopie/A21.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jonas\Documents\Praktikum-IV\A21 - rentgen - kopie\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCF08714-37AB-489B-918E-9A08D2C7FFD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{281F1E5C-253E-44C5-A1A3-F9B72471ABCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B8DF00CB-DCF1-4C1A-ABA1-0DE29D1463BD}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="39">
   <si>
     <t>Fitování lineárních grafů 1. úkolu</t>
   </si>
@@ -150,6 +150,9 @@
   </si>
   <si>
     <t>dtheta/dlambda / mm^(-1)</t>
+  </si>
+  <si>
+    <t>sigma lambda</t>
   </si>
 </sst>
 </file>
@@ -157,7 +160,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="167" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -189,11 +192,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normální" xfId="0" builtinId="0"/>
@@ -528,7 +532,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59B71BA6-80FA-438B-B425-C6D36BB24D85}">
-  <dimension ref="A3:H42"/>
+  <dimension ref="A3:I42"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
@@ -538,14 +542,15 @@
     <col min="6" max="6" width="10.88671875" customWidth="1"/>
     <col min="7" max="7" width="15.6640625" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>1</v>
       </c>
@@ -562,7 +567,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B5">
         <v>-372.9</v>
       </c>
@@ -585,7 +590,7 @@
         <v>8.071654024064876E-34</v>
       </c>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B6">
         <v>-391.6</v>
       </c>
@@ -600,7 +605,7 @@
         <v>25000</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B7">
         <v>-533.4</v>
       </c>
@@ -615,7 +620,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B8">
         <v>-629.70000000000005</v>
       </c>
@@ -630,7 +635,7 @@
         <v>33000</v>
       </c>
     </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>6</v>
       </c>
@@ -652,8 +657,11 @@
       <c r="H11" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I11" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>11</v>
       </c>
@@ -678,8 +686,12 @@
         <f>1/SQRT(F12)</f>
         <v>8.5403081136830428E-2</v>
       </c>
-    </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I12" s="4">
+        <f>2*201.4*COS(D12*0.0174532925)*0.0174532925</f>
+        <v>6.6104006333476555</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C13">
         <v>44.4</v>
       </c>
@@ -701,8 +713,12 @@
         <f t="shared" ref="H13:H31" si="3">1/SQRT(F13)</f>
         <v>8.1058927047863744E-2</v>
       </c>
-    </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I13" s="4">
+        <f t="shared" ref="I13:I31" si="4">2*201.4*COS(D13*0.0174532925)*0.0174532925</f>
+        <v>6.509042627084745</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>14</v>
       </c>
@@ -724,8 +740,12 @@
         <f t="shared" si="3"/>
         <v>8.5403081136830428E-2</v>
       </c>
-    </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I14" s="4">
+        <f t="shared" si="4"/>
+        <v>6.6104006333476555</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C15">
         <v>44.2</v>
       </c>
@@ -744,8 +764,12 @@
         <f t="shared" si="3"/>
         <v>8.1232883430024966E-2</v>
       </c>
-    </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I15" s="4">
+        <f t="shared" si="4"/>
+        <v>6.5136688134298719</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C16">
         <v>86.6</v>
       </c>
@@ -767,8 +791,12 @@
         <f t="shared" si="3"/>
         <v>8.5087490598633714E-2</v>
       </c>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I16" s="4">
+        <f>2*201.4*COS(D16*0.0174532925)*0.0174532925/2</f>
+        <v>2.5581890078044345</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C17">
         <v>99.1</v>
       </c>
@@ -790,8 +818,12 @@
         <f t="shared" si="3"/>
         <v>8.0776644206137435E-2</v>
       </c>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I17" s="4">
+        <f>2*201.4*COS(D17*0.0174532925)*0.0174532925/2</f>
+        <v>2.2805369500175878</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>15</v>
       </c>
@@ -813,8 +845,12 @@
         <f t="shared" si="3"/>
         <v>8.5403081136830428E-2</v>
       </c>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I18" s="4">
+        <f t="shared" si="4"/>
+        <v>6.6104006333476555</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C19">
         <v>44.4</v>
       </c>
@@ -833,8 +869,12 @@
         <f t="shared" si="3"/>
         <v>8.1058927047863744E-2</v>
       </c>
-    </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I19" s="4">
+        <f t="shared" si="4"/>
+        <v>6.509042627084745</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>16</v>
       </c>
@@ -856,8 +896,12 @@
         <f t="shared" si="3"/>
         <v>8.5403081136830428E-2</v>
       </c>
-    </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I20" s="4">
+        <f t="shared" si="4"/>
+        <v>6.6104006333476555</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C21">
         <v>44.4</v>
       </c>
@@ -876,8 +920,12 @@
         <f t="shared" si="3"/>
         <v>8.1058927047863744E-2</v>
       </c>
-    </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I21" s="4">
+        <f t="shared" si="4"/>
+        <v>6.509042627084745</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>17</v>
       </c>
@@ -902,8 +950,12 @@
         <f t="shared" si="3"/>
         <v>7.5525795647888166E-2</v>
       </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I22" s="4">
+        <f t="shared" si="4"/>
+        <v>6.3294086209930702</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C23">
         <v>57.2</v>
       </c>
@@ -925,8 +977,12 @@
         <f t="shared" si="3"/>
         <v>7.2015710369590563E-2</v>
       </c>
-    </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I23" s="4">
+        <f t="shared" si="4"/>
+        <v>6.1723838162898943</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>18</v>
       </c>
@@ -948,8 +1004,12 @@
         <f t="shared" si="3"/>
         <v>7.566256237227606E-2</v>
       </c>
-    </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I24" s="4">
+        <f t="shared" si="4"/>
+        <v>6.3347392591187281</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C25">
         <v>57.2</v>
       </c>
@@ -968,8 +1028,12 @@
         <f t="shared" si="3"/>
         <v>7.2015710369590563E-2</v>
       </c>
-    </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I25" s="4">
+        <f t="shared" si="4"/>
+        <v>6.1723838162898943</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>19</v>
       </c>
@@ -994,8 +1058,12 @@
         <f t="shared" si="3"/>
         <v>0.12811265858695886</v>
       </c>
-    </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I26" s="4">
+        <f t="shared" si="4"/>
+        <v>6.949296100792659</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C27">
         <v>19.600000000000001</v>
       </c>
@@ -1017,8 +1085,12 @@
         <f t="shared" si="3"/>
         <v>0.12077119745804396</v>
       </c>
-    </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I27" s="4">
+        <f t="shared" si="4"/>
+        <v>6.9276010282462526</v>
+      </c>
+    </row>
+    <row r="28" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C28">
         <v>35.5</v>
       </c>
@@ -1040,8 +1112,12 @@
         <f t="shared" si="3"/>
         <v>0.12761948342760282</v>
       </c>
-    </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I28" s="4">
+        <f>2*201.4*COS(D28*0.0174532925)*0.0174532925/2</f>
+        <v>3.3477599132221791</v>
+      </c>
+    </row>
+    <row r="29" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C29">
         <v>40.5</v>
       </c>
@@ -1063,8 +1139,12 @@
         <f t="shared" si="3"/>
         <v>0.11977295540570206</v>
       </c>
-    </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I29" s="4">
+        <f>2*201.4*COS(D29*0.0174532925)*0.0174532925/2</f>
+        <v>3.2978299007850631</v>
+      </c>
+    </row>
+    <row r="30" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
         <v>24</v>
       </c>
@@ -1083,8 +1163,12 @@
         <f t="shared" si="3"/>
         <v>0.12138611272327374</v>
       </c>
-    </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I30" s="4">
+        <f t="shared" si="4"/>
+        <v>6.929678944638094</v>
+      </c>
+    </row>
+    <row r="31" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
         <v>25</v>
       </c>
@@ -1102,6 +1186,10 @@
       <c r="H31">
         <f t="shared" si="3"/>
         <v>8.5403081136830428E-2</v>
+      </c>
+      <c r="I31" s="4">
+        <f t="shared" si="4"/>
+        <v>6.6104006333476555</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
